--- a/simulations/all_dig_inv2_VF.xlsx
+++ b/simulations/all_dig_inv2_VF.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\simulations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02A9E758-C0B4-408E-88E1-91B1D7076750}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA70CB75-1661-4509-B14A-1312559F86D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6350" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2455,7 +2455,7 @@
         <v>93.51</v>
       </c>
       <c r="AK3" s="4">
-        <v>-651101.69874275709</v>
+        <v>-651101.69874275697</v>
       </c>
       <c r="AL3" s="4">
         <v>-479036.53667522129</v>
@@ -2666,7 +2666,7 @@
         <v>-579266.27008729789</v>
       </c>
       <c r="AL4" s="4">
-        <v>-684134.54392147821</v>
+        <v>-684134.54392147798</v>
       </c>
       <c r="AM4" s="4">
         <v>-6.3517927378926764</v>
